--- a/연구코드/aec/results/신촌/logistic_results.xlsx
+++ b/연구코드/aec/results/신촌/logistic_results.xlsx
@@ -710,7 +710,7 @@
         <v>8.9108</v>
       </c>
       <c r="C2" t="n">
-        <v>7411.3487</v>
+        <v>7411.3489</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -1052,7 +1052,7 @@
         <v>105.3565</v>
       </c>
       <c r="C21" t="n">
-        <v>5.698362895386974e+45</v>
+        <v>5.698367857291181e+45</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -1286,7 +1286,7 @@
         <v>117.6051</v>
       </c>
       <c r="C34" t="n">
-        <v>1.189168026865881e+51</v>
+        <v>1.189169163028276e+51</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -1502,7 +1502,7 @@
         <v>113.8601</v>
       </c>
       <c r="C46" t="n">
-        <v>2.810777264241634e+49</v>
+        <v>2.810780034252235e+49</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
@@ -1592,7 +1592,7 @@
         <v>100.0617</v>
       </c>
       <c r="C51" t="n">
-        <v>2.859289574977098e+43</v>
+        <v>2.859291974418416e+43</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
@@ -1610,7 +1610,7 @@
         <v>84.91030000000001</v>
       </c>
       <c r="C52" t="n">
-        <v>7.517643574938535e+36</v>
+        <v>7.517649154081424e+36</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
@@ -1646,7 +1646,7 @@
         <v>176.5196</v>
       </c>
       <c r="C54" t="n">
-        <v>4.586562914514311e+76</v>
+        <v>4.586569879261268e+76</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7221</v>
+        <v>0.723</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6881</v>
+        <v>0.6916</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7531</v>
+        <v>0.7542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/연구코드/aec/results/신촌/logistic_results.xlsx
+++ b/연구코드/aec/results/신촌/logistic_results.xlsx
@@ -469,19 +469,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.0681</v>
+        <v>1.0496</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8275</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>1.3787</v>
+        <v>1.3535</v>
       </c>
       <c r="E2" t="n">
-        <v>0.612907</v>
+        <v>0.708856</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5082</v>
+        <v>0.506</v>
       </c>
     </row>
     <row r="3">
@@ -491,19 +491,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.4412</v>
+        <v>1.4085</v>
       </c>
       <c r="C3" t="n">
-        <v>1.2506</v>
+        <v>1.2243</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6609</v>
+        <v>1.6205</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6147</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="4">
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.7147</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6037</v>
+        <v>0.6147</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8188</v>
+        <v>0.831</v>
       </c>
       <c r="E4" t="n">
-        <v>6e-06</v>
+        <v>1.3e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5944</v>
+        <v>0.5911</v>
       </c>
     </row>
     <row r="5">
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.0964</v>
+        <v>1.0977</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9674</v>
+        <v>0.969</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2425</v>
+        <v>1.2435</v>
       </c>
       <c r="E5" t="n">
-        <v>0.149725</v>
+        <v>0.142766</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5356</v>
+        <v>0.5354</v>
       </c>
     </row>
     <row r="6">
@@ -557,19 +557,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9473</v>
+        <v>0.9337</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8349</v>
+        <v>0.8235</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0748</v>
+        <v>1.0587</v>
       </c>
       <c r="E6" t="n">
-        <v>0.400678</v>
+        <v>0.284671</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5169</v>
+        <v>0.5195</v>
       </c>
     </row>
     <row r="7">
@@ -579,19 +579,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.722</v>
+        <v>0.7146</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5026</v>
+        <v>0.4977</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0371</v>
+        <v>1.026</v>
       </c>
       <c r="E7" t="n">
-        <v>0.077919</v>
+        <v>0.068587</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5577</v>
+        <v>0.5587</v>
       </c>
     </row>
     <row r="8">
@@ -601,19 +601,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6937</v>
+        <v>0.7052</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.6083</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8055</v>
+        <v>0.8176</v>
       </c>
       <c r="E8" t="n">
-        <v>2e-06</v>
+        <v>4e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5988</v>
+        <v>0.595</v>
       </c>
     </row>
     <row r="9">
@@ -624,7 +624,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LR_χ²=69.56</t>
+          <t>LR_χ²=69.278</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.010866</v>
+        <v>0.011525</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6017</v>
+        <v>0.601</v>
       </c>
     </row>
   </sheetData>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.9108</v>
+        <v>9.4649</v>
       </c>
       <c r="C2" t="n">
-        <v>7411.3489</v>
+        <v>12899.2322</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1489</v>
+        <v>0.1301</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1606</v>
+        <v>1.1389</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4272</v>
+        <v>0.4047</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5329</v>
+        <v>1.4988</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9794</v>
+        <v>0.9344</v>
       </c>
       <c r="C5" t="n">
-        <v>2.6629</v>
+        <v>2.5457</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -779,10 +779,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3017</v>
+        <v>0.3117</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3522</v>
+        <v>1.3658</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.1432</v>
+        <v>-0.1646</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8665</v>
+        <v>0.8482</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5446</v>
+        <v>0.448</v>
       </c>
       <c r="C8" t="n">
-        <v>1.724</v>
+        <v>1.5652</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.7924</v>
+        <v>-1.7026</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1666</v>
+        <v>0.1822</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-81.6677</v>
+        <v>-59.6554</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-10.4092</v>
+        <v>-10.9597</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-39.9416</v>
+        <v>-30.8664</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-168.5773</v>
+        <v>-119.1707</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-10.7408</v>
+        <v>-11.2648</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-52.0151</v>
+        <v>-38.3475</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-26.5489</v>
+        <v>-21.2884</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-9.401199999999999</v>
+        <v>-9.953900000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-69.7624</v>
+        <v>-51.4219</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-41.1846</v>
+        <v>-31.655</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-9.972</v>
+        <v>-9.8588</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>105.3565</v>
+        <v>78.82850000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>5.698367857291181e+45</v>
+        <v>1.716968078656334e+34</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-49.4268</v>
+        <v>-35.8644</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-82.8691</v>
+        <v>-60.5009</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-17.2414</v>
+        <v>-15.162</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-77.714</v>
+        <v>-56.9541</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-8.3691</v>
+        <v>-8.8009</v>
       </c>
       <c r="C26" t="n">
         <v>0.0002</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-62.3162</v>
+        <v>-46.1676</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-10.5004</v>
+        <v>-10.9351</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-9.369</v>
+        <v>-9.988</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-25.0115</v>
+        <v>-20.3628</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-150.7856</v>
+        <v>-105.973</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -1247,10 +1247,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-9.6699</v>
+        <v>-10.2338</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
@@ -1265,7 +1265,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-8.9626</v>
+        <v>-9.555400000000001</v>
       </c>
       <c r="C33" t="n">
         <v>0.0001</v>
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>117.6051</v>
+        <v>86.5277</v>
       </c>
       <c r="C34" t="n">
-        <v>1.189169163028276e+51</v>
+        <v>3.788851904569629e+37</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-46.0376</v>
+        <v>-34.7924</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-43.812</v>
+        <v>-33.223</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-60.6388</v>
+        <v>-45.7754</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-10.0363</v>
+        <v>-10.576</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-10.2901</v>
+        <v>-10.7973</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-10.3451</v>
+        <v>-10.8788</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-41.8123</v>
+        <v>-32.3954</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-45.6609</v>
+        <v>-35.0719</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-10.9442</v>
+        <v>-11.4686</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-9.9175</v>
+        <v>-10.4508</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-10.9757</v>
+        <v>-11.4635</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>113.8601</v>
+        <v>84.3107</v>
       </c>
       <c r="C46" t="n">
-        <v>2.810780034252235e+49</v>
+        <v>4.127154817710314e+36</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
@@ -1517,7 +1517,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-70.49550000000001</v>
+        <v>-51.8129</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-29.0795</v>
+        <v>-23.4123</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-9.481999999999999</v>
+        <v>-10.0423</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-11.3951</v>
+        <v>-11.8935</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>100.0617</v>
+        <v>73.0669</v>
       </c>
       <c r="C51" t="n">
-        <v>2.859291974418416e+43</v>
+        <v>5.402119189622802e+31</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>84.91030000000001</v>
+        <v>63.0605</v>
       </c>
       <c r="C52" t="n">
-        <v>7.517649154081424e+36</v>
+        <v>2.436904777127218e+27</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-10.3286</v>
+        <v>-10.867</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>176.5196</v>
+        <v>126.7785</v>
       </c>
       <c r="C54" t="n">
-        <v>4.586569879261268e+76</v>
+        <v>1.146105009935585e+55</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.723</v>
+        <v>0.717</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6916</v>
+        <v>0.6847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7542</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2496</v>
+        <v>0.2623</v>
       </c>
       <c r="C9" t="inlineStr"/>
     </row>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6975</v>
+        <v>0.653</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.6807</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3953</v>
+        <v>0.4051</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.8549</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="C14" t="inlineStr"/>
     </row>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>616</v>
+        <v>648</v>
       </c>
       <c r="C15" t="inlineStr"/>
     </row>
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>335</v>
+        <v>304</v>
       </c>
       <c r="C16" t="inlineStr"/>
     </row>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="C17" t="inlineStr"/>
     </row>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6.3538</v>
+        <v>7.5705</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.607666</v>
+        <v>0.476505</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1755</v>
+        <v>0.1698</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1625</v>
+        <v>0.164</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1364.49</v>
+        <v>1378.14</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1637.06</v>
+        <v>1650.88</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/연구코드/aec/results/신촌/logistic_results.xlsx
+++ b/연구코드/aec/results/신촌/logistic_results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,23 +509,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AEC: p25 (표준화)</t>
+          <t>AEC: mean (표준화)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7147</v>
+        <v>0.7052</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6147</v>
+        <v>0.6083</v>
       </c>
       <c r="D4" t="n">
-        <v>0.831</v>
+        <v>0.8176</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3e-05</v>
+        <v>4e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5911</v>
+        <v>0.595</v>
       </c>
     </row>
     <row r="5">
@@ -597,50 +597,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AEC: mean (표준화)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.7052</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.6083</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.8176</v>
+          <t>ManufacturerModelName (LR χ²-test)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LR_χ²=69.278</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>4e-06</v>
+        <v>0.011525</v>
       </c>
       <c r="F8" t="n">
-        <v>0.595</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ManufacturerModelName (LR χ²-test)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>LR_χ²=69.278</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.011525</v>
-      </c>
-      <c r="F9" t="n">
         <v>0.601</v>
       </c>
     </row>
@@ -655,7 +633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,10 +685,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.4649</v>
+        <v>8.9537</v>
       </c>
       <c r="C2" t="n">
-        <v>12899.2322</v>
+        <v>7736.8133</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -725,10 +703,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1301</v>
+        <v>0.1492</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1389</v>
+        <v>1.161</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -743,10 +721,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4047</v>
+        <v>0.4086</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4988</v>
+        <v>1.5047</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -757,14 +735,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>p25_z</t>
+          <t>mean_z</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9344</v>
+        <v>-0.8146</v>
       </c>
       <c r="C5" t="n">
-        <v>2.5457</v>
+        <v>0.4428</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -779,10 +757,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3117</v>
+        <v>0.1914</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3658</v>
+        <v>1.211</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -797,10 +775,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.1646</v>
+        <v>-0.2013</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8482</v>
+        <v>0.8177</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -815,10 +793,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.448</v>
+        <v>0.404</v>
       </c>
       <c r="C8" t="n">
-        <v>1.5652</v>
+        <v>1.4978</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -829,14 +807,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mean_z</t>
+          <t>Model_Alexion</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.7026</v>
+        <v>-63.7224</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1822</v>
+        <v>0</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -847,11 +825,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Model_Alexion</t>
+          <t>Model_Aquilion</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-59.6554</v>
+        <v>-10.39</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -865,11 +843,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Model_Aquilion</t>
+          <t>Model_Aquilion Lightning</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-10.9597</v>
+        <v>-32.6659</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -883,11 +861,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Model_Aquilion Lightning</t>
+          <t>Model_Aquilion ONE</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-30.8664</v>
+        <v>-140.4866</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -901,11 +879,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Model_Aquilion ONE</t>
+          <t>Model_Aquilion PRIME</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-119.1707</v>
+        <v>-10.7821</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -919,11 +897,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Model_Aquilion PRIME</t>
+          <t>Model_Aquilion/LB</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-11.2648</v>
+        <v>-41.5108</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -937,11 +915,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Model_Aquilion/LB</t>
+          <t>Model_Brilliance 40</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-38.3475</v>
+        <v>-22.6468</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -955,14 +933,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Model_Brilliance 40</t>
+          <t>Model_Brilliance 64</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-21.2884</v>
+        <v>-9.473800000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -973,11 +951,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Model_Brilliance 64</t>
+          <t>Model_Brivo CT385 Series</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-9.953900000000001</v>
+        <v>-56.4728</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -991,11 +969,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Model_Brivo CT385 Series</t>
+          <t>Model_Definition Edge</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-51.4219</v>
+        <v>-33.0154</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -1009,14 +987,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Model_Definition Edge</t>
+          <t>Model_Discovery CT750 HD</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-31.655</v>
+        <v>-9.3721</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
@@ -1027,14 +1005,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Model_Discovery CT750 HD</t>
+          <t>Model_ECLOS</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-9.8588</v>
+        <v>81.8073</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0001</v>
+        <v>3.376308537713601e+35</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
@@ -1045,14 +1023,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Model_ECLOS</t>
+          <t>Model_Emotion 16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>78.82850000000001</v>
+        <v>-37.9813</v>
       </c>
       <c r="C21" t="n">
-        <v>1.716968078656334e+34</v>
+        <v>0</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -1063,11 +1041,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Model_Emotion 16</t>
+          <t>Model_Emotion 16 (2007)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-35.8644</v>
+        <v>-60.9322</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -1081,11 +1059,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Model_Emotion 16 (2007)</t>
+          <t>Model_GMS Revolution FT</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-60.5009</v>
+        <v>-14.782</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -1099,11 +1077,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Model_GMS Revolution FT</t>
+          <t>Model_Ingenuity CT</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-15.162</v>
+        <v>-62.435</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -1117,14 +1095,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Model_Ingenuity CT</t>
+          <t>Model_Ingenuity CT Elite</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-56.9541</v>
+        <v>-8.319000000000001</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
@@ -1135,14 +1113,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Model_Ingenuity CT Elite</t>
+          <t>Model_Ingenuity Core</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-8.8009</v>
+        <v>-52.6313</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
@@ -1153,11 +1131,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Model_Ingenuity Core</t>
+          <t>Model_Ingenuity Core 128</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-46.1676</v>
+        <v>-10.3871</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -1171,14 +1149,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Model_Ingenuity Core 128</t>
+          <t>Model_LightSpeed VCT</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-10.9351</v>
+        <v>-9.494999999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
@@ -1189,11 +1167,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Model_LightSpeed VCT</t>
+          <t>Model_MX 16</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-9.988</v>
+        <v>-20.6352</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -1207,11 +1185,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Model_MX 16</t>
+          <t>Model_Optima CT660</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-20.3628</v>
+        <v>-109.4724</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -1225,14 +1203,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Model_Optima CT660</t>
+          <t>Model_Revolution CT</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-105.973</v>
+        <v>-9.738099999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
@@ -1243,14 +1221,14 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Model_Revolution CT</t>
+          <t>Model_Revolution EVO</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-10.2338</v>
+        <v>-9.0695</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
@@ -1261,14 +1239,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Model_Revolution EVO</t>
+          <t>Model_Revolution Frontier</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-9.555400000000001</v>
+        <v>90.6695</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0001</v>
+        <v>2.38372765539329e+39</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
@@ -1279,14 +1257,14 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Model_Revolution Frontier</t>
+          <t>Model_Revolution HD</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>86.5277</v>
+        <v>-37.1503</v>
       </c>
       <c r="C34" t="n">
-        <v>3.788851904569629e+37</v>
+        <v>0</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -1297,11 +1275,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Model_Revolution HD</t>
+          <t>Model_SOMATOM Definition</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-34.7924</v>
+        <v>-37.5086</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -1315,11 +1293,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition</t>
+          <t>Model_SOMATOM Definition AS</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-33.223</v>
+        <v>-44.4749</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -1333,11 +1311,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition AS</t>
+          <t>Model_SOMATOM Definition AS+</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-45.7754</v>
+        <v>-10.1083</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -1351,11 +1329,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition AS+</t>
+          <t>Model_SOMATOM Definition Edge</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-10.576</v>
+        <v>-10.2912</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -1369,11 +1347,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition Edge</t>
+          <t>Model_SOMATOM Definition Flash</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-10.7973</v>
+        <v>-10.3771</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -1387,11 +1365,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition Flash</t>
+          <t>Model_SOMATOM Drive</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-10.8788</v>
+        <v>-33.5099</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -1405,11 +1383,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Drive</t>
+          <t>Model_SOMATOM Emotion 16</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-32.3954</v>
+        <v>-36.9868</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -1423,11 +1401,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Emotion 16</t>
+          <t>Model_SOMATOM Force</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-35.0719</v>
+        <v>-10.951</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -1441,11 +1419,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Force</t>
+          <t>Model_SOMATOM Perspective</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-11.4686</v>
+        <v>-9.922499999999999</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -1459,11 +1437,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Perspective</t>
+          <t>Model_SOMATOM Scope</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-10.4508</v>
+        <v>-10.9834</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -1477,14 +1455,14 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Scope</t>
+          <t>Model_SOMATOM go.Top</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-11.4635</v>
+        <v>95.9709</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>4.7823828248599e+41</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
@@ -1495,14 +1473,14 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Model_SOMATOM go.Top</t>
+          <t>Model_Scope</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>84.3107</v>
+        <v>-52.6658</v>
       </c>
       <c r="C46" t="n">
-        <v>4.127154817710314e+36</v>
+        <v>0</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
@@ -1513,11 +1491,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Model_Scope</t>
+          <t>Model_Sensation 16</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-51.8129</v>
+        <v>-23.4482</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -1531,14 +1509,14 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Model_Sensation 16</t>
+          <t>Model_Sensation 64</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-23.4123</v>
+        <v>-9.4754</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
@@ -1549,11 +1527,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Model_Sensation 64</t>
+          <t>Model_Sensation Open</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-10.0423</v>
+        <v>-11.2379</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -1567,14 +1545,14 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Model_Sensation Open</t>
+          <t>Model_Spirit</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-11.8935</v>
+        <v>79.57559999999999</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>3.624389978327152e+34</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
@@ -1585,14 +1563,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Model_Spirit</t>
+          <t>Model_Supria</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>73.0669</v>
+        <v>76.6622</v>
       </c>
       <c r="C51" t="n">
-        <v>5.402119189622802e+31</v>
+        <v>1.967838284017359e+33</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
@@ -1603,14 +1581,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Model_Supria</t>
+          <t>Model_iCT 256</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>63.0605</v>
+        <v>-10.37</v>
       </c>
       <c r="C52" t="n">
-        <v>2.436904777127218e+27</v>
+        <v>0</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
@@ -1621,38 +1599,20 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Model_iCT 256</t>
+          <t>Model_iCT SP</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-10.867</v>
+        <v>130.0186</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>2.92650164539254e+56</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Model_iCT SP</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>126.7785</v>
-      </c>
-      <c r="C54" t="n">
-        <v>1.146105009935585e+55</v>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1752,7 +1712,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6847</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1767,7 +1727,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.7487</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1793,7 +1753,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2623</v>
+        <v>0.2452</v>
       </c>
       <c r="C9" t="inlineStr"/>
     </row>
@@ -1804,7 +1764,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.653</v>
+        <v>0.694</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1819,7 +1779,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6807</v>
+        <v>0.6324</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1834,7 +1794,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4051</v>
+        <v>0.386</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,7 +1809,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8549</v>
+        <v>0.8612</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1864,7 +1824,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="C14" t="inlineStr"/>
     </row>
@@ -1875,7 +1835,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>648</v>
+        <v>602</v>
       </c>
       <c r="C15" t="inlineStr"/>
     </row>
@@ -1886,7 +1846,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>304</v>
+        <v>350</v>
       </c>
       <c r="C16" t="inlineStr"/>
     </row>
@@ -1897,7 +1857,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="C17" t="inlineStr"/>
     </row>
@@ -1908,7 +1868,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7.5705</v>
+        <v>5.2493</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1923,7 +1883,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.476505</v>
+        <v>0.73063</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1951,7 +1911,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1698</v>
+        <v>0.1681</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1966,7 +1926,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.164</v>
+        <v>0.1638</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1981,7 +1941,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1378.14</v>
+        <v>1377.83</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1996,7 +1956,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1650.88</v>
+        <v>1645.42</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2011,7 +1971,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C25" t="inlineStr"/>
     </row>
